--- a/imageCreationExcel/Bright/Master/MASTER_8.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_8.xlsx
@@ -606,15 +606,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\2_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M_8_2_A_filler_2_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_2_A_filler_2_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -768,15 +774,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>M_8_5_9_unmatch_0_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_8_5_9_unmatch_0_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -822,15 +834,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>M_8_6_R_filler_4_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_6_R_filler_4_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -984,15 +1002,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>M_8_9_0_match_0_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_8_9_0_match_0_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1092,15 +1116,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\1_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>M_8_11_E_filler_1_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_11_E_filler_1_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1146,15 +1176,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>M_8_12_2_unmatch_4_day_sun_empty_MODEL.jpg</t>
+          <t>M_8_12_2_unmatch_4_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1200,15 +1248,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\6_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>M_8_13_L_filler_6_day_sun_busy_MODEL.jpg</t>
+          <t>M_8_13_L_filler_6_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1308,15 +1374,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>M_8_15_F_filler_1_day_rain_empty_MODEL.jpg</t>
+          <t>M_8_15_F_filler_1_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1416,15 +1500,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>M_8_17_J_filler_8_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_17_J_filler_8_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1470,15 +1560,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>M_8_18_S_filler_6_day_rain_busy_MODEL.jpg</t>
+          <t>M_8_18_S_filler_6_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1524,15 +1632,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\2_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>M_8_19_Q_filler_2_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_19_Q_filler_2_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1578,15 +1692,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\8_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>M_8_20_J_filler_8_day_rain_busy_MODEL.jpg</t>
+          <t>M_8_20_J_filler_8_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1740,15 +1872,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>M_8_23_0_match_0_day_rain_busy_MODEL.jpg</t>
+          <t>M_8_23_0_match_0_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1794,15 +1944,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\0_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>M_8_24_P_filler_0_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_24_P_filler_0_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1848,15 +2004,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>M_8_25_U_filler_0_day_sun_busy_MODEL.jpg</t>
+          <t>M_8_25_U_filler_0_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1902,15 +2076,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\6_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>M_8_26_6_match_6_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_26_6_match_6_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2064,15 +2244,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>M_8_29_D_filler_2_day_sun_empty_MODEL.jpg</t>
+          <t>M_8_29_D_filler_2_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2226,15 +2424,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>M_8_32_C_filler_6_day_rain_busy_MODEL.jpg</t>
+          <t>M_8_32_C_filler_6_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2280,15 +2496,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>M_8_33_6_unmatch_7_day_sun_empty_MODEL.jpg</t>
+          <t>M_8_33_6_unmatch_7_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2388,15 +2622,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\8_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>M_8_35_I_filler_8_day_rain_busy_MODEL.jpg</t>
+          <t>M_8_35_I_filler_8_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2442,15 +2694,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>M_8_36_3_unmatch_1_day_rain_empty_MODEL.jpg</t>
+          <t>M_8_36_3_unmatch_1_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,15 +2766,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\0_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>M_8_37_A_filler_0_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_8_37_A_filler_0_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2826,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>M_8_38_U_filler_6_day_rain_busy_MODEL.jpg</t>
+          <t>M_8_38_U_filler_6_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2604,15 +2898,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>M_8_39_4_match_4_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_39_4_match_4_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2658,15 +2958,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>M_8_40_C_filler_3_day_sun_busy_MODEL.jpg</t>
+          <t>M_8_40_C_filler_3_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2712,15 +3030,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>M_8_41_Q_filler_1_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_8_41_Q_filler_1_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2766,15 +3090,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\5_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>M_8_42_A_filler_5_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_42_A_filler_5_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2820,15 +3150,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>M_8_43_7_match_7_day_sun_empty_MODEL.jpg</t>
+          <t>M_8_43_7_match_7_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2874,15 +3222,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>M_8_44_I_filler_3_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_8_44_I_filler_3_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2928,15 +3282,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\5_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>M_8_45_E_filler_5_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_45_E_filler_5_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2982,15 +3342,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>M_8_46_8_match_8_day_sun_empty_MODEL.jpg</t>
+          <t>M_8_46_8_match_8_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -3090,15 +3468,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>M_8_48_1_unmatch_4_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_8_48_1_unmatch_4_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
